--- a/output/pdf_financials_xlsx/MMX.xlsx
+++ b/output/pdf_financials_xlsx/MMX.xlsx
@@ -4125,34 +4125,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.259174</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.460402</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.226924</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.998745</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.302237</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.631587</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.704287</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.914644</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.925324</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.925324</v>
       </c>
     </row>
     <row r="93">
@@ -6416,7 +6416,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -8306,7 +8310,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -11354,7 +11362,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>0.259174</v>
       </c>
@@ -11608,7 +11620,11 @@
           <t>Reserves (Note 2 &amp; 11)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.259174</v>
       </c>

--- a/output/pdf_financials_xlsx/MMX.xlsx
+++ b/output/pdf_financials_xlsx/MMX.xlsx
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.008151</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.019574</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.019794</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008437</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.03904</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.126661</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.084401</v>
+        <v>-1.092552</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.480025</v>
+        <v>-0.499599</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.209441</v>
+        <v>-2.229235</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.9794349999999999</v>
+        <v>-0.987872</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.431805</v>
+        <v>-0.470845</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-23.150374</v>
+        <v>-23.277035</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.057134</v>
+        <v>-1.065285</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.349763</v>
+        <v>-0.369337</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.993182</v>
+        <v>-2.012976</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1719,13 +1719,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.957735</v>
+        <v>-0.966172</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.413916</v>
+        <v>-0.452956</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-23.135467</v>
+        <v>-23.262128</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1219.835683459879</v>
+        <v>-1229.241189910226</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-137.9817346194055</v>
+        <v>-145.7036905536817</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-622.7895800850516</v>
+        <v>-628.9744126533787</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -9930,7 +9930,11 @@
           <t>Reclamation deposits (Note 4(l))</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
         <v>0.033348</v>
       </c>
@@ -10836,7 +10840,11 @@
           <t>Reclamation deposits (Note 3(l))</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -14526,7 +14534,11 @@
           <t>Unrealized foreign exchange on reclamation deposit</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="n">
         <v>-0.003114</v>
       </c>
@@ -15942,7 +15954,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -17774,7 +17790,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -18356,7 +18372,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">

--- a/output/pdf_financials_xlsx/MMX.xlsx
+++ b/output/pdf_financials_xlsx/MMX.xlsx
@@ -2010,34 +2010,34 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.325358</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.184723</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.39578</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.173151</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.098922</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.030352</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.016312</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>0.009312000000000001</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>0.019008</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>0.019486</v>
       </c>
     </row>
     <row r="38">
@@ -2158,34 +2158,34 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.325358</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.184723</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.39578</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.173151</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.098922</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.030352</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.016312</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.009312000000000001</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.019008</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.019486</v>
       </c>
     </row>
     <row r="42">
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.82364</v>
+        <v>2.498282</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.181474</v>
+        <v>3.996751</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.23701</v>
+        <v>2.84123</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.24032</v>
+        <v>0.06716900000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.145265</v>
+        <v>0.046343</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.060085</v>
+        <v>0.029733</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.0293</v>
+        <v>0.012988</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.044929</v>
+        <v>0.035617</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.053884</v>
+        <v>0.034876</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.056435</v>
+        <v>0.036949</v>
       </c>
     </row>
     <row r="49">
@@ -4946,16 +4946,16 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.125642</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.7771169999999999</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.836716</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.030345</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -14986,7 +14986,11 @@
           <t>Net proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E147" s="5" t="n">
         <v>0.125642</v>
       </c>
